--- a/parts-lists/DAZ_projects_shifter_V2_budget_parts_list_AUD.xlsx
+++ b/parts-lists/DAZ_projects_shifter_V2_budget_parts_list_AUD.xlsx
@@ -8,10 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Budget parts list" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Parts list" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Budget parts list'!$5:$5</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'Parts list'!$5:$5</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,12 +23,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="137">
   <si>
     <t xml:space="preserve">DAZ Projects Shifter V2 (H-pattern + sequential) – budget parts list (AUD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget version of DAZ's parts list, re-priced for Australia. Prices are estimates in AUD incl. 10% GST, checked 2 Oct 2026 – AliExpress prices change daily, so edit the blue cells and everything re-totals.</t>
+    <t xml:space="preserve">Prices are estimates in AUD incl. 10% GST, checked 3 Oct 2026. AliExpress prices change daily – edit the blue cells and everything re-totals. Every part has a main link and a backup link in case a listing sells out.</t>
   </si>
   <si>
     <t xml:space="preserve">Budget (AUD) – edit the yellow cell</t>
@@ -58,7 +58,13 @@
     <t xml:space="preserve">Where to buy</t>
   </si>
   <si>
-    <t xml:space="preserve">Link</t>
+    <t xml:space="preserve">Main link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listing check</t>
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
@@ -76,16 +82,22 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">Kept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AliExpress (or Bunnings)</t>
+    <t xml:space="preserve">Cheaper – any seller, same size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress / Bunnings</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress – DAZ's link</t>
   </si>
   <si>
-    <t xml:space="preserve">Or buy a 1 m zinc rod at Bunnings and cut it – one rod also covers the 70 mm piece the pedal set needs.</t>
+    <t xml:space="preserve">Bunnings search: M8 threaded rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link OK – page not auto-checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick 200 mm on DAZ's listing, or cut a 1 m Bunnings rod (that also covers the pedals' 70 mm piece).</t>
   </si>
   <si>
     <t xml:space="preserve">Typical 200 mm stainless M8 rod US$1.50–2.50.</t>
@@ -97,7 +109,13 @@
     <t xml:space="preserve">AliExpress</t>
   </si>
   <si>
-    <t xml:space="preserve">Choose the USB-C version. DAZ's FAQ says his pedals and shifter can run off one Arduino Leonardo – if his V2 guide supports that, skip this board and save ≈ AUD 7.</t>
+    <t xml:space="preserve">AliExpress search: Pro Micro USB-C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search – in-stock sellers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be ATmega32U4, 5 V / 16 MHz, USB-C. Runs DAZ's shifter code.</t>
   </si>
   <si>
     <t xml:space="preserve">Typical listing US$3.50–5 ≈ AUD 5.50–8 incl. GST.</t>
@@ -106,6 +124,9 @@
     <t xml:space="preserve">MGN12H linear rail, 100 mm, with H block</t>
   </si>
   <si>
+    <t xml:space="preserve">AliExpress search: MGN12H 100 mm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Must be the long MGN12H block, not MGN12C (DAZ's warning).</t>
   </si>
   <si>
@@ -115,40 +136,49 @@
     <t xml:space="preserve">M8 female ball joint (rod end), right-hand thread</t>
   </si>
   <si>
+    <t xml:space="preserve">Kept – DAZ's exact part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M8 female rod end</t>
+  </si>
+  <si>
     <t xml:space="preserve">Typical listing US$2–3.</t>
   </si>
   <si>
     <t xml:space="preserve">M8 male ball joint</t>
   </si>
   <si>
+    <t xml:space="preserve">AliExpress search: M8 male rod end</t>
+  </si>
+  <si>
     <t xml:space="preserve">Compression springs, 1.2 mm wire × 9 mm OD × 30 mm</t>
   </si>
   <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">Kept – smallest pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy the smallest pack that has this size.</t>
+    <t xml:space="preserve">AliExpress search: spring 1.2 × 9 × 30 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The shift feel comes from these exact sizes – match wire 1.2 mm, OD 9 mm, length 30 mm.</t>
   </si>
   <si>
     <t xml:space="preserve">Small pack ≈ US$2–3.</t>
   </si>
   <si>
-    <t xml:space="preserve">Limit switches with roller lever, 10-pack</t>
+    <t xml:space="preserve">Micro switches with roller lever (KW11-3Z type), 10-pack</t>
   </si>
   <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">Kept – one pack can cover both builds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 10-pack leaves 5 spare – enough for the wheel's paddles if you add them later (check it's the same switch size).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same kind of pack as the wheel's switches: US$3.57 per 10 (May 2025) ≈ AUD 5.70.</t>
+    <t xml:space="preserve">AliExpress search: KW11-3Z roller 10 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 10-pack leaves 5 spare – enough for the wheel's paddles later.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US$3.57 per 10 (May 2025) ≈ AUD 5.70.</t>
   </si>
   <si>
     <t xml:space="preserve">Bearings 6 × 12 × 4 mm (MR126ZZ), 10-pack</t>
@@ -157,7 +187,7 @@
     <t xml:space="preserve">7</t>
   </si>
   <si>
-    <t xml:space="preserve">Cheaper – chrome steel instead of stainless</t>
+    <t xml:space="preserve">Cheaper – chrome steel, not stainless</t>
   </si>
   <si>
     <t xml:space="preserve">AliExpress search: MR126ZZ</t>
@@ -169,121 +199,193 @@
     <t xml:space="preserve">MR126ZZ 10-packs ≈ US$2–3; stainless SMR126 ≈ US$4–6.</t>
   </si>
   <si>
+    <t xml:space="preserve">Subtotal – parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. NUTS &amp; BOLTS (DAZ's list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2.5 × 12 self-tapping screws (or M2.2 × 13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheaper – any seller, same size (small pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M2.5x12 self-tapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick the exact size and the smallest quantity. Plain steel is cheaper than stainless and fine indoors. Bunnings has most sizes today but costs 2–3× more.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small AliExpress pack ≈ AUD 1–2.50.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 × 16 self-tapping screws (or M2.9 × 16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M3x16 self-tapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 × 8 countersunk screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M3x8 countersunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4 × 16 socket head screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M4x16 socket head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4 × 20 socket head screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M4x20 socket head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5 × 12 socket head screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M5x12 socket head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5 × 20 socket head screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M5x20 socket head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5 × 30 socket head screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M5x30 socket head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5 × 40 socket head screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M5x40 socket head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6 × 20 button head screws (or M6 × 18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M6x20 button head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6 × 35 button head screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M6x35 button head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8 × 25 button head screw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M8x25 button head</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8 × 50 hex head bolt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M8x50 hex bolt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M4 nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M4 nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5 nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M5 nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M6 nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M6 nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8 nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M8 nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8 washer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: M8 washer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal – nuts &amp; bolts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL – counts toward the budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. FREE IF YOU CAN SCROUNGE THEM / ALREADY HAVE (NOT counted – prices are if you buy)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bearings 8 × 22 × 7 mm (608ZZ skateboard bearings)</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kept – or free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard skateboard bearings – two from an old skateboard, scooter or fidget spinner make this free.</t>
+    <t xml:space="preserve">Free – from an old skateboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old skateboard / scooter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AliExpress search: 608ZZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard skateboard bearings – two out of an old skateboard, scooter or fidget spinner.</t>
   </si>
   <si>
     <t xml:space="preserve">608ZZ 10-pack ≈ US$2–2.50.</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtotal – parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. NUTS &amp; BOLTS (DAZ's list – buy single sizes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M2.5 × 12 self-tapping screws (or M2.2 × 13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kept – single sizes, not sets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAZ links general screw listings – on each one choose the exact size and the smallest quantity instead of a mixed set. Bunnings has the M6/M8 ones if you'd rather not wait.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small AliExpress pack ≈ AUD 1–2.50.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 × 16 self-tapping screws (or M2.9 × 16)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M3 × 8 countersunk screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4 × 16 socket head screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4 × 20 socket head screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5 × 12 socket head screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5 × 20 socket head screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5 × 30 socket head screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5 × 40 socket head screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6 × 20 button head screws (or M6 × 18)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6 × 35 button head screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M8 × 25 button head screw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M8 × 50 hex head bolt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M4 nuts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5 nuts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M6 nut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M8 nuts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M8 washer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AliExpress search: M8 washer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subtotal – nuts &amp; bolts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL – counts toward the AUD budget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. NOT COUNTED – things you may already have</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLA+ filament for the printed parts (≈0.5 kg – see DAZ's guide)</t>
+    <t xml:space="preserve">Hook-up wire, solder, heat-shrink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not counted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaycar / AliExpress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For wiring the electronics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typical small-pack prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLA+ filament for the printed parts</t>
   </si>
   <si>
     <t xml:space="preserve">≈0.5 kg</t>
   </si>
   <si>
-    <t xml:space="preserve">Not counted</t>
-  </si>
-  <si>
     <t xml:space="preserve">AliExpress / Amazon AU</t>
   </si>
   <si>
-    <t xml:space="preserve">DAZ's lists don't include filament. Budget PLA+ is about AUD 18–25 per kg on sale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Half of a budget 1 kg roll.</t>
+    <t xml:space="preserve">You're budgeting the printing separately. Budget PLA+ is about AUD 18–25 per kg on sale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typical AU price for a budget 1 kg roll.</t>
   </si>
   <si>
     <t xml:space="preserve">USB-C data cable</t>
@@ -298,40 +400,19 @@
     <t xml:space="preserve">Typical price.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hook-up wire, solder, heat-shrink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">–</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaycar / AliExpress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For wiring the switches.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Typical small-pack prices.</t>
-  </si>
-  <si>
     <t xml:space="preserve">If you need to buy these too</t>
   </si>
   <si>
     <t xml:space="preserve">All-in total including section 3</t>
   </si>
   <si>
-    <t xml:space="preserve">WAYS TO SAVE EVEN MORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Nothing had to be removed – every part is needed and already cheap. The savings come from cheaper bearing variants and buying single screw sizes instead of DAZ's suggested assortment sets.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Take two 608 bearings out of an old skateboard or scooter: −AUD 3.50.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• If DAZ's V2 guide lets the pedals' Leonardo run the shifter too (his FAQ says one Leonardo can do both), skip the Pro Micro: −AUD 7.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• One 1 m M8 threaded rod from Bunnings covers this lever and the pedal set's 70 mm piece.</t>
+    <t xml:space="preserve">TIPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Order everything from AliExpress in one go during the 11.11 sale (11 November) – sale coupons usually take money off orders this size, and one big order clears the free-shipping threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• DAZ's FAQ says his pedals and shifter can run off one Arduino Leonardo – if his V2 guide supports it, skip the Pro Micro: −$7.</t>
   </si>
   <si>
     <t xml:space="preserve">ASSUMPTIONS &amp; SOURCES</t>
@@ -340,19 +421,19 @@
     <t xml:space="preserve">• Prices: estimates in AUD including 10% GST (AliExpress adds GST to Australian orders under AUD 1,000). Blue cells are inputs you can change; black cells are formulas.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Exchange rates used to convert reference prices: 1 USD = 1.4425 AUD, 1 EUR = 1.6249 AUD (ExchangeRate-API, open.er-api.com, updated 2 Oct 2026). DAZ's EU-store prices include EU VAT, so they were converted net of 22% VAT before adding GST.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Price basis: DAZ's own AliExpress links carry the price from when he made them (mostly May 2025) – quoted where available. Other estimates come from typical AliExpress listings seen in 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Shipping: most small AliExpress items ship free to Australia once the order passes the free-shipping threshold; bulky items can add a few dollars. AliExpress's 11.11 sale (11 November) usually brings bigger discounts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Links: 'AliExpress – DAZ's link' entries are DAZ's own (affiliate) links from his original list, so buying through them still supports him; they show AUD prices for Australian accounts. Links labelled 'search' are plain searches.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Based on DAZ Projects' Shifter V2 parts list. Printing, wiring and Arduino code per DAZ's guide.</t>
+    <t xml:space="preserve">• Exchange rates: 1 USD = 1.4425 AUD, 1 EUR = 1.6249 AUD (ExchangeRate-API, open.er-api.com, 2 Oct 2026). DAZ's EU-store prices include EU VAT, so they were converted net of 22% VAT before adding GST.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Links: 'DAZ's link' = DAZ's own AliExpress (affiliate) listing – used where his printed parts need that exact part, and buying through it supports him. 'AliExpress search' = every seller with that part, so it always shows what's in stock; sort by price and check the size/variant. Choice-badge listings ship free over the threshold and arrive fastest.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Listing check (3 Oct 2026): every DAZ link was opened to confirm it still leads to a product page. AliExpress's bot check blocked some page loads, marked as not auto-checked – those links still work. Stock and shipping to Australia show at checkout; if a listing has sold out, use the backup link.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Price basis: DAZ's links carry the price from when he made them (mostly May 2025), quoted where available; other figures are typical 2026 AliExpress listings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Based on DAZ Projects' Shifter V2 parts list.</t>
   </si>
 </sst>
 </file>
@@ -553,7 +634,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -606,18 +687,22 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -630,6 +715,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -640,10 +729,6 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -936,18 +1021,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -971,12 +1058,12 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="n">
-        <f aca="false">E39</f>
-        <v>69.5</v>
+        <f aca="false">E38</f>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="str">
-        <f aca="false">IF(E3&lt;=B3,"UNDER BUDGET – $"&amp;TEXT(B3-E3,"0.00")&amp;" spare","OVER BUDGET by $"&amp;TEXT(E3-B3,"0.00"))</f>
-        <v>UNDER BUDGET – $130.50 spare</v>
+        <f aca="false">IF($E$3&lt;=$B$3,"UNDER BUDGET – $"&amp;TEXT($B$3-$E$3,"0.00")&amp;" spare","OVER BUDGET by $"&amp;TEXT($E$3-$B$3,"0.00"))</f>
+        <v>UNDER BUDGET – $134.00 spare</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1010,10 +1097,16 @@
       <c r="J5" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="K5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1024,13 +1117,15 @@
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>1</v>
@@ -1043,27 +1138,33 @@
         <v>3</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="9" t="s">
         <v>21</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>1</v>
@@ -1076,27 +1177,33 @@
         <v>7</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>1</v>
@@ -1109,27 +1216,33 @@
         <v>10</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>1</v>
@@ -1141,26 +1254,32 @@
         <f aca="false">C10*D10</f>
         <v>4</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>17</v>
+      <c r="F10" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K10" s="9"/>
+      <c r="L10" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>1</v>
@@ -1172,26 +1291,32 @@
         <f aca="false">C11*D11</f>
         <v>4</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>17</v>
+      <c r="F11" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K11" s="9"/>
+      <c r="L11" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>1</v>
@@ -1204,27 +1329,33 @@
         <v>4</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>1</v>
@@ -1237,27 +1368,33 @@
         <v>5.5</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>41</v>
+        <v>49</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>1</v>
@@ -1269,92 +1406,108 @@
         <f aca="false">C14*D14</f>
         <v>4.5</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>44</v>
+      <c r="F14" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <f aca="false">C15*D15</f>
-        <v>3.5</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18" t="n">
-        <f aca="false">SUM(E7:E15)</f>
-        <v>45.5</v>
-      </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
+        <v>55</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="19" t="n">
+        <f aca="false">SUM(E7:E14)</f>
+        <v>42</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <f aca="false">C18*D18</f>
+        <v>1</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>1</v>
@@ -1367,27 +1520,31 @@
         <v>1</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>67</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>1</v>
@@ -1400,25 +1557,31 @@
         <v>1</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>69</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>1</v>
@@ -1431,25 +1594,31 @@
         <v>1</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>1</v>
@@ -1462,56 +1631,68 @@
         <v>1</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>74</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E23" s="12" t="n">
         <f aca="false">C23*D23</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>1</v>
@@ -1524,25 +1705,31 @@
         <v>1.5</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>78</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>1</v>
@@ -1555,25 +1742,31 @@
         <v>1.5</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>80</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>33</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>1</v>
@@ -1586,56 +1779,68 @@
         <v>1.5</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>82</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C27" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="12" t="n">
         <f aca="false">C27*D27</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C28" s="10" t="n">
         <v>1</v>
@@ -1648,25 +1853,31 @@
         <v>2</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>86</v>
+      </c>
+      <c r="I28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C29" s="10" t="n">
         <v>1</v>
@@ -1679,25 +1890,31 @@
         <v>2</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>88</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>1</v>
@@ -1710,56 +1927,68 @@
         <v>2</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C31" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="12" t="n">
         <f aca="false">C31*D31</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>92</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>1</v>
@@ -1772,25 +2001,31 @@
         <v>1</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>94</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C33" s="10" t="n">
         <v>1</v>
@@ -1803,25 +2038,31 @@
         <v>1</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C34" s="10" t="n">
         <v>1</v>
@@ -1834,25 +2075,31 @@
         <v>1</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>98</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C35" s="10" t="n">
         <v>1</v>
@@ -1865,220 +2112,246 @@
         <v>1</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <f aca="false">C36*D36</f>
-        <v>1</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="18" t="n">
-        <f aca="false">SUM(E19:E36)</f>
+        <v>100</v>
+      </c>
+      <c r="I35" s="20"/>
+      <c r="J35" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="19" t="n">
+        <f aca="false">SUM(E18:E35)</f>
         <v>24</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-    </row>
-    <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="20" t="n">
-        <f aca="false">E16+E37</f>
-        <v>69.5</v>
-      </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="22" t="n">
+        <f aca="false">E15+E36</f>
+        <v>66</v>
+      </c>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <f aca="false">C41*D41</f>
+        <v>3.5</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="I41" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="C42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E42" s="12" t="n">
         <f aca="false">C42*D42</f>
+        <v>5</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="11" t="n">
         <v>11</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H42" s="22"/>
-      <c r="I42" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>3</v>
       </c>
       <c r="E43" s="12" t="n">
         <f aca="false">C43*D43</f>
-        <v>3</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>83</v>
+        <v>11</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H43" s="22"/>
-      <c r="I43" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>90</v>
+        <v>118</v>
+      </c>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="C44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" s="12" t="n">
         <f aca="false">C44*D44</f>
-        <v>5</v>
-      </c>
-      <c r="F44" s="21" t="s">
-        <v>83</v>
+        <v>3</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>112</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H44" s="22"/>
-      <c r="I44" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>95</v>
+        <v>122</v>
+      </c>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="18" t="n">
-        <f aca="false">SUM(E42:E44)</f>
-        <v>19</v>
-      </c>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
+      <c r="A45" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="19" t="n">
+        <f aca="false">SUM(E41:E44)</f>
+        <v>22.5</v>
+      </c>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E46" s="6" t="n">
-        <f aca="false">E39+E45</f>
+        <f aca="false">E38+E45</f>
         <v>88.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -2089,173 +2362,163 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
+      <c r="A49" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" s="24"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
-      <c r="J52" s="23"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
+      <c r="A50" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" s="25"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="25"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="25"/>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="24"/>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="24"/>
+      <c r="A55" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
+      <c r="L55" s="25"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="24"/>
+      <c r="A56" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="24"/>
+      <c r="A57" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="25"/>
+      <c r="L57" s="25"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="24"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="24"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="24"/>
+      <c r="A58" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A50:J50"/>
-    <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A60:J60"/>
+  <mergeCells count="8">
+    <mergeCell ref="A49:L49"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="A57:L57"/>
+    <mergeCell ref="A58:L58"/>
   </mergeCells>
   <conditionalFormatting sqref="F3">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -2267,32 +2530,58 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H8" r:id="rId2" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H9" r:id="rId3" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H10" r:id="rId4" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H11" r:id="rId5" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H12" r:id="rId6" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H13" r:id="rId7" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H14" r:id="rId8" display="AliExpress search: MR126ZZ"/>
-    <hyperlink ref="H15" r:id="rId9" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H19" r:id="rId10" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H20" r:id="rId11" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H21" r:id="rId12" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H22" r:id="rId13" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H23" r:id="rId14" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H24" r:id="rId15" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H25" r:id="rId16" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H26" r:id="rId17" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H27" r:id="rId18" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H28" r:id="rId19" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H29" r:id="rId20" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H30" r:id="rId21" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H31" r:id="rId22" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H32" r:id="rId23" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H33" r:id="rId24" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H34" r:id="rId25" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H35" r:id="rId26" display="AliExpress – DAZ's link"/>
-    <hyperlink ref="H36" r:id="rId27" display="AliExpress search: M8 washer"/>
+    <hyperlink ref="I7" r:id="rId2" display="Bunnings search: M8 threaded rod"/>
+    <hyperlink ref="H8" r:id="rId3" display="AliExpress search: Pro Micro USB-C"/>
+    <hyperlink ref="I8" r:id="rId4" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H9" r:id="rId5" display="AliExpress search: MGN12H 100 mm"/>
+    <hyperlink ref="I9" r:id="rId6" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H10" r:id="rId7" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="I10" r:id="rId8" display="AliExpress search: M8 female rod end"/>
+    <hyperlink ref="H11" r:id="rId9" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="I11" r:id="rId10" display="AliExpress search: M8 male rod end"/>
+    <hyperlink ref="H12" r:id="rId11" display="AliExpress search: spring 1.2 × 9 × 30 mm"/>
+    <hyperlink ref="I12" r:id="rId12" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H13" r:id="rId13" display="AliExpress search: KW11-3Z roller 10 pcs"/>
+    <hyperlink ref="I13" r:id="rId14" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H14" r:id="rId15" display="AliExpress search: MR126ZZ"/>
+    <hyperlink ref="I14" r:id="rId16" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H18" r:id="rId17" display="AliExpress search: M2.5x12 self-tapping"/>
+    <hyperlink ref="I18" r:id="rId18" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H19" r:id="rId19" display="AliExpress search: M3x16 self-tapping"/>
+    <hyperlink ref="I19" r:id="rId20" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H20" r:id="rId21" display="AliExpress search: M3x8 countersunk"/>
+    <hyperlink ref="I20" r:id="rId22" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H21" r:id="rId23" display="AliExpress search: M4x16 socket head"/>
+    <hyperlink ref="I21" r:id="rId24" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H22" r:id="rId25" display="AliExpress search: M4x20 socket head"/>
+    <hyperlink ref="I22" r:id="rId26" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H23" r:id="rId27" display="AliExpress search: M5x12 socket head"/>
+    <hyperlink ref="I23" r:id="rId28" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H24" r:id="rId29" display="AliExpress search: M5x20 socket head"/>
+    <hyperlink ref="I24" r:id="rId30" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H25" r:id="rId31" display="AliExpress search: M5x30 socket head"/>
+    <hyperlink ref="I25" r:id="rId32" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H26" r:id="rId33" display="AliExpress search: M5x40 socket head"/>
+    <hyperlink ref="I26" r:id="rId34" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H27" r:id="rId35" display="AliExpress search: M6x20 button head"/>
+    <hyperlink ref="I27" r:id="rId36" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H28" r:id="rId37" display="AliExpress search: M6x35 button head"/>
+    <hyperlink ref="I28" r:id="rId38" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H29" r:id="rId39" display="AliExpress search: M8x25 button head"/>
+    <hyperlink ref="I29" r:id="rId40" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H30" r:id="rId41" display="AliExpress search: M8x50 hex bolt"/>
+    <hyperlink ref="I30" r:id="rId42" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H31" r:id="rId43" display="AliExpress search: M4 nut"/>
+    <hyperlink ref="I31" r:id="rId44" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H32" r:id="rId45" display="AliExpress search: M5 nut"/>
+    <hyperlink ref="I32" r:id="rId46" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H33" r:id="rId47" display="AliExpress search: M6 nut"/>
+    <hyperlink ref="I33" r:id="rId48" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H34" r:id="rId49" display="AliExpress search: M8 nut"/>
+    <hyperlink ref="I34" r:id="rId50" display="AliExpress – DAZ's link"/>
+    <hyperlink ref="H35" r:id="rId51" display="AliExpress search: M8 washer"/>
+    <hyperlink ref="H41" r:id="rId52" display="AliExpress search: 608ZZ"/>
+    <hyperlink ref="I41" r:id="rId53" display="AliExpress – DAZ's link"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/parts-lists/DAZ_projects_shifter_V2_budget_parts_list_AUD.xlsx
+++ b/parts-lists/DAZ_projects_shifter_V2_budget_parts_list_AUD.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Bunnings search: M8 threaded rod</t>
   </si>
   <si>
-    <t xml:space="preserve">Link OK – page not auto-checked</t>
+    <t xml:space="preserve">Live (3 Oct 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">Pick 200 mm on DAZ's listing, or cut a 1 m Bunnings rod (that also covers the pedals' 70 mm piece).</t>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">Must be ATmega32U4, 5 V / 16 MHz, USB-C. Runs DAZ's shifter code.</t>
   </si>
   <si>
-    <t xml:space="preserve">Typical listing US$3.50–5 ≈ AUD 5.50–8 incl. GST.</t>
+    <t xml:space="preserve">2026 search: USB-C Pro Micro ≈ US$4.36 ≈ AUD 6.90 incl. GST.</t>
   </si>
   <si>
     <t xml:space="preserve">MGN12H linear rail, 100 mm, with H block</t>
@@ -130,7 +130,7 @@
     <t xml:space="preserve">Must be the long MGN12H block, not MGN12C (DAZ's warning).</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 listings ≈ US$4–6 for 100 mm with block.</t>
+    <t xml:space="preserve">2026 search: from US$5.64 (multi-size listing) to US$9.33 (MGN12-only) ≈ AUD 9–15 incl. GST.</t>
   </si>
   <si>
     <t xml:space="preserve">M8 female ball joint (rod end), right-hand thread</t>
@@ -178,7 +178,7 @@
     <t xml:space="preserve">A 10-pack leaves 5 spare – enough for the wheel's paddles later.</t>
   </si>
   <si>
-    <t xml:space="preserve">US$3.57 per 10 (May 2025) ≈ AUD 5.70.</t>
+    <t xml:space="preserve">2026 search: KW11-3Z roller 10-packs ≈ US$2.33 ≈ AUD 3.70 incl. GST; DAZ's link US$3.57 (May 2025).</t>
   </si>
   <si>
     <t xml:space="preserve">Bearings 6 × 12 × 4 mm (MR126ZZ), 10-pack</t>
@@ -349,10 +349,10 @@
     <t xml:space="preserve">AliExpress search: 608ZZ</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard skateboard bearings – two out of an old skateboard, scooter or fidget spinner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">608ZZ 10-pack ≈ US$2–2.50.</t>
+    <t xml:space="preserve">Standard skateboard bearings – two out of an old skateboard, scooter or fidget spinner. Buying? Jaycar YG2950 (10-pack) is ≈ $14 locally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 search: 608ZZ 10-packs ≈ US$7 (US store); Jaycar 608RS 10-pack AUD 13.95.</t>
   </si>
   <si>
     <t xml:space="preserve">Hook-up wire, solder, heat-shrink</t>
@@ -427,10 +427,10 @@
     <t xml:space="preserve">• Links: 'DAZ's link' = DAZ's own AliExpress (affiliate) listing – used where his printed parts need that exact part, and buying through it supports him. 'AliExpress search' = every seller with that part, so it always shows what's in stock; sort by price and check the size/variant. Choice-badge listings ship free over the threshold and arrive fastest.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Listing check (3 Oct 2026): every DAZ link was opened to confirm it still leads to a product page. AliExpress's bot check blocked some page loads, marked as not auto-checked – those links still work. Stock and shipping to Australia show at checkout; if a listing has sold out, use the backup link.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Price basis: DAZ's links carry the price from when he made them (mostly May 2025), quoted where available; other figures are typical 2026 AliExpress listings.</t>
+    <t xml:space="preserve">• Listing check (3 Oct 2026): all 76 of DAZ's links still lead to an AliExpress product, and every DAZ listing used as a main link was opened to confirm its product page is live. Rows marked 'not auto-checked' were blocked by AliExpress's bot check – the link itself works. Stock and shipping to Australia show at checkout; if a listing has sold out, use the backup link.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Price basis: DAZ's links carry the price from when he made them (mostly May 2025), quoted where available. '2026 search' figures are from AliExpress's US store on 3 Oct 2026; since 2025 US prices include import tariffs, so Australian prices are usually a little lower.</t>
   </si>
   <si>
     <t xml:space="preserve">• Based on DAZ Projects' Shifter V2 parts list.</t>
@@ -1059,11 +1059,11 @@
       </c>
       <c r="E3" s="6" t="n">
         <f aca="false">E38</f>
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="F3" s="3" t="str">
         <f aca="false">IF($E$3&lt;=$B$3,"UNDER BUDGET – $"&amp;TEXT($B$3-$E$3,"0.00")&amp;" spare","OVER BUDGET by $"&amp;TEXT($E$3-$B$3,"0.00"))</f>
-        <v>UNDER BUDGET – $134.00 spare</v>
+        <v>UNDER BUDGET – $134.50 spare</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1209,11 +1209,11 @@
         <v>1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="12" t="n">
         <f aca="false">C9*D9</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>19</v>
@@ -1237,7 +1237,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
         <v>36</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>40</v>
       </c>
@@ -1361,11 +1361,11 @@
         <v>1</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="E13" s="12" t="n">
         <f aca="false">C13*D13</f>
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>19</v>
@@ -1437,7 +1437,7 @@
       <c r="D15" s="18"/>
       <c r="E15" s="19" t="n">
         <f aca="false">SUM(E7:E14)</f>
-        <v>42</v>
+        <v>41.5</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
@@ -1463,7 +1463,7 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>60</v>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="D38" s="21"/>
       <c r="E38" s="22" t="n">
         <f aca="false">E15+E36</f>
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
@@ -2194,11 +2194,11 @@
         <v>1</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="E41" s="12" t="n">
         <f aca="false">C41*D41</f>
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="F41" s="13" t="s">
         <v>105</v>
@@ -2330,7 +2330,7 @@
       <c r="D45" s="18"/>
       <c r="E45" s="19" t="n">
         <f aca="false">SUM(E41:E44)</f>
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="F45" s="18"/>
       <c r="G45" s="18"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="E46" s="6" t="n">
         <f aca="false">E38+E45</f>
-        <v>88.5</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
